--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-dispense-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-dispense-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Cette entrée de type supply permet de décrire un traitement dispensé avec notamment le médicament dispensé, la quantité et la référence de la prescription.</t>
+    <t>FrMedicationDispenseDocument permet de décrire un traitement dispensé avec notamment le médicament dispensé, la quantité et la référence de la prescription.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -384,7 +384,7 @@
 </t>
   </si>
   <si>
-    <t>Texte de l'entrée</t>
+    <t>Partie narrative</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -475,7 +475,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l'entrée.</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
